--- a/education_forms/046_student_allergy_registration_form--education_forms.xlsx
+++ b/education_forms/046_student_allergy_registration_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'peanut',_'value':_'peanut'}</t>
+          <t>peanut</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Peanut', 'value': 'peanut'}</t>
+          <t>Peanut</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'tree_nut',_'value':_'tree_nut'}</t>
+          <t>tree_nut</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Tree Nut', 'value': 'tree_nut'}</t>
+          <t>Tree Nut</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'fish',_'value':_'fish'}</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Fish', 'value': 'fish'}</t>
+          <t>Fish</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'shellfish',_'value':_'shellfish'}</t>
+          <t>shellfish</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Shellfish', 'value': 'shellfish'}</t>
+          <t>Shellfish</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'mild',_'value':_1}</t>
+          <t>mild</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Mild', 'value': 1}</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'moderate',_'value':_2}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate', 'value': 2}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'severe',_'value':_3}</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Severe', 'value': 3}</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
